--- a/docs/04-review/po-pdf-guides-vs-site-comparison.xlsx
+++ b/docs/04-review/po-pdf-guides-vs-site-comparison.xlsx
@@ -580,7 +580,7 @@
     <row r="3" ht="8" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PO reference guides (7 regional PDFs, Oct 2026) compared field-by-field against app/src/data/content/kshetrams.json. Details: 'Temple Index', 'Side-by-Side', 'Differences'.</t>
+          <t>PO reference guides (7 regional PDFs, Oct 2026) compared field-by-field against app/src/data/content/kshetrams.json. Details: 'Temple Index', 'Side-by-Side', 'Differences'. PO ruling (2026-10-18): where the PDF-extracted details and the site dataset clash, the PDF-extracted details are the point of truth.</t>
         </is>
       </c>
     </row>
